--- a/salidas/empresas/DIS.xlsx
+++ b/salidas/empresas/DIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.26825714111328</v>
+        <v>22.26825523376465</v>
       </c>
       <c r="C3" t="n">
         <v>27.61213493347168</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>22.18869590759277</v>
+        <v>22.18869781494141</v>
       </c>
       <c r="C4" t="n">
         <v>27.51348495483398</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.24438858032227</v>
+        <v>22.2443904876709</v>
       </c>
       <c r="C5" t="n">
         <v>27.58254051208496</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.2651538848877</v>
+        <v>24.26515769958496</v>
       </c>
       <c r="C6" t="n">
         <v>30.08824920654297</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>23.86736297607422</v>
+        <v>23.86736679077148</v>
       </c>
       <c r="C7" t="n">
         <v>29.59499931335449</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>24.59134483337402</v>
+        <v>24.59134674072266</v>
       </c>
       <c r="C10" t="n">
         <v>30.49271583557129</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>26.29388618469238</v>
+        <v>26.29388046264648</v>
       </c>
       <c r="C12" t="n">
         <v>32.60382461547852</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>27.51140594482422</v>
+        <v>27.51141166687012</v>
       </c>
       <c r="C13" t="n">
         <v>33.80735397338867</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>28.23391532897949</v>
+        <v>28.23391723632812</v>
       </c>
       <c r="C14" t="n">
         <v>34.69520568847656</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>27.49535179138184</v>
+        <v>27.49534797668457</v>
       </c>
       <c r="C15" t="n">
         <v>33.78762435913086</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>27.63985633850098</v>
+        <v>27.63985443115234</v>
       </c>
       <c r="C16" t="n">
         <v>33.96519470214844</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>28.08139228820801</v>
+        <v>28.08138465881348</v>
       </c>
       <c r="C17" t="n">
         <v>34.50777053833008</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.45066261291504</v>
+        <v>28.4506721496582</v>
       </c>
       <c r="C18" t="n">
         <v>34.9615592956543</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.78210258483887</v>
+        <v>27.78210067749023</v>
       </c>
       <c r="C19" t="n">
         <v>34.13999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>26.85440826416016</v>
+        <v>26.85440063476562</v>
       </c>
       <c r="C20" t="n">
         <v>33</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>27.34267425537109</v>
+        <v>27.34267044067383</v>
       </c>
       <c r="C21" t="n">
         <v>33.59999847412109</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>27.98554611206055</v>
+        <v>27.98554801940918</v>
       </c>
       <c r="C22" t="n">
         <v>34.38999938964844</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.18085479736328</v>
+        <v>28.18084716796875</v>
       </c>
       <c r="C23" t="n">
         <v>34.63000106811523</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>26.97647094726562</v>
+        <v>26.97647285461426</v>
       </c>
       <c r="C24" t="n">
         <v>33.15000152587891</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>26.55224990844727</v>
+        <v>26.55225372314453</v>
       </c>
       <c r="C25" t="n">
         <v>32.27999877929688</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.54521179199219</v>
+        <v>24.54520606994629</v>
       </c>
       <c r="C26" t="n">
         <v>29.84000015258789</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>26.65918922424316</v>
+        <v>26.65918350219727</v>
       </c>
       <c r="C27" t="n">
         <v>32.40999984741211</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.81195259094238</v>
+        <v>25.81195068359375</v>
       </c>
       <c r="C28" t="n">
         <v>31.3799991607666</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.67564010620117</v>
+        <v>26.67563819885254</v>
       </c>
       <c r="C29" t="n">
         <v>32.43000030517578</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>27.63804054260254</v>
+        <v>27.63803672790527</v>
       </c>
       <c r="C30" t="n">
         <v>33.59999847412109</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.66389656066895</v>
+        <v>25.66389083862305</v>
       </c>
       <c r="C31" t="n">
         <v>31.20000076293945</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>24.9647159576416</v>
+        <v>24.96471405029297</v>
       </c>
       <c r="C32" t="n">
         <v>30.35000038146973</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.60984039306641</v>
+        <v>26.60983657836914</v>
       </c>
       <c r="C33" t="n">
         <v>32.34999847412109</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.24438667297363</v>
+        <v>25.244384765625</v>
       </c>
       <c r="C34" t="n">
         <v>30.69000053405762</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.31254386901855</v>
+        <v>21.31254196166992</v>
       </c>
       <c r="C35" t="n">
         <v>25.90999984741211</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>18.5240650177002</v>
+        <v>18.52407073974609</v>
       </c>
       <c r="C36" t="n">
         <v>22.52000045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.94365882873535</v>
+        <v>18.94365692138672</v>
       </c>
       <c r="C37" t="n">
         <v>22.69000053405762</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.26552772521973</v>
+        <v>17.26552963256836</v>
       </c>
       <c r="C38" t="n">
         <v>20.68000030517578</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.16160774230957</v>
+        <v>15.1616039276123</v>
       </c>
       <c r="C40" t="n">
         <v>18.15999984741211</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.28409576416016</v>
+        <v>18.28409385681152</v>
       </c>
       <c r="C41" t="n">
         <v>21.89999961853027</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>20.22104644775391</v>
+        <v>20.22104263305664</v>
       </c>
       <c r="C42" t="n">
         <v>24.21999931335449</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>19.47798538208008</v>
+        <v>19.47799110412598</v>
       </c>
       <c r="C43" t="n">
         <v>23.32999992370605</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>20.97244453430176</v>
+        <v>20.97243690490723</v>
       </c>
       <c r="C44" t="n">
         <v>25.1200008392334</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>21.74054336547852</v>
+        <v>21.74053955078125</v>
       </c>
       <c r="C45" t="n">
         <v>26.04000091552734</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>22.92608833312988</v>
+        <v>22.92608451843262</v>
       </c>
       <c r="C46" t="n">
         <v>27.45999908447266</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>22.85094451904297</v>
+        <v>22.85094261169434</v>
       </c>
       <c r="C47" t="n">
         <v>27.3700008392334</v>
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.2357120513916</v>
+        <v>27.23571586608887</v>
       </c>
       <c r="C49" t="n">
         <v>32.25</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>24.95551872253418</v>
+        <v>24.95551681518555</v>
       </c>
       <c r="C50" t="n">
         <v>29.54999923706055</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>26.38274955749512</v>
+        <v>26.38275337219238</v>
       </c>
       <c r="C51" t="n">
         <v>31.23999977111816</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.48212814331055</v>
+        <v>29.48213195800781</v>
       </c>
       <c r="C52" t="n">
         <v>34.90999984741211</v>
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.22380256652832</v>
+        <v>28.22380065917969</v>
       </c>
       <c r="C54" t="n">
         <v>33.41999816894531</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>26.60232353210449</v>
+        <v>26.60232925415039</v>
       </c>
       <c r="C55" t="n">
         <v>31.5</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>28.45181846618652</v>
+        <v>28.45182228088379</v>
       </c>
       <c r="C56" t="n">
         <v>33.68999862670898</v>
@@ -1605,7 +1617,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.95355033874512</v>
+        <v>27.95355606079102</v>
       </c>
       <c r="C58" t="n">
         <v>33.09999847412109</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.512451171875</v>
+        <v>30.51244354248047</v>
       </c>
       <c r="C59" t="n">
         <v>36.13000106811523</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.83336639404297</v>
+        <v>30.8333625793457</v>
       </c>
       <c r="C60" t="n">
         <v>36.5099983215332</v>
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>32.02437591552734</v>
+        <v>32.02436447143555</v>
       </c>
       <c r="C61" t="n">
         <v>37.5099983215332</v>
@@ -1738,11 +1750,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>33.18547439575195</v>
+        <v>33.18547058105469</v>
       </c>
       <c r="C62" t="n">
         <v>38.86999893188477</v>
@@ -1767,7 +1779,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1796,7 +1808,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1825,11 +1837,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.79685974121094</v>
+        <v>36.7968635559082</v>
       </c>
       <c r="C65" t="n">
         <v>43.09999847412109</v>
@@ -1854,11 +1866,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>35.54185104370117</v>
+        <v>35.54183959960938</v>
       </c>
       <c r="C66" t="n">
         <v>41.63000106811523</v>
@@ -1883,7 +1895,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1912,11 +1924,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>32.97203826904297</v>
+        <v>32.97203063964844</v>
       </c>
       <c r="C68" t="n">
         <v>38.61999893188477</v>
@@ -1941,11 +1953,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>29.07891845703125</v>
+        <v>29.07891464233398</v>
       </c>
       <c r="C69" t="n">
         <v>34.06000137329102</v>
@@ -1970,7 +1982,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1999,11 +2011,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>29.77899360656738</v>
+        <v>29.77899551391602</v>
       </c>
       <c r="C71" t="n">
         <v>34.88000106811523</v>
@@ -2028,11 +2040,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>30.60713577270508</v>
+        <v>30.60713958740234</v>
       </c>
       <c r="C72" t="n">
         <v>35.84999847412109</v>
@@ -2057,11 +2069,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.553466796875</v>
+        <v>32.55346298217773</v>
       </c>
       <c r="C73" t="n">
         <v>37.5</v>
@@ -2086,7 +2098,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2115,7 +2127,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2144,7 +2156,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2173,7 +2185,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2202,11 +2214,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.68050003051758</v>
+        <v>39.68049240112305</v>
       </c>
       <c r="C78" t="n">
         <v>45.70999908447266</v>
@@ -2231,7 +2243,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2260,11 +2272,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>42.65806198120117</v>
+        <v>42.65805435180664</v>
       </c>
       <c r="C80" t="n">
         <v>49.13999938964844</v>
@@ -2289,11 +2301,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>42.94451522827148</v>
+        <v>42.94452667236328</v>
       </c>
       <c r="C81" t="n">
         <v>49.47000122070312</v>
@@ -2318,11 +2330,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>45.38385391235352</v>
+        <v>45.38386917114258</v>
       </c>
       <c r="C82" t="n">
         <v>52.27999877929688</v>
@@ -2347,11 +2359,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>42.64069747924805</v>
+        <v>42.64068603515625</v>
       </c>
       <c r="C83" t="n">
         <v>49.11999893188477</v>
@@ -2376,7 +2388,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2405,11 +2417,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>43.88605117797852</v>
+        <v>43.88604736328125</v>
       </c>
       <c r="C85" t="n">
         <v>49.79000091552734</v>
@@ -2434,11 +2446,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>47.49106216430664</v>
+        <v>47.49107360839844</v>
       </c>
       <c r="C86" t="n">
         <v>53.88000106811523</v>
@@ -2463,11 +2475,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>48.11688613891602</v>
+        <v>48.11687850952148</v>
       </c>
       <c r="C87" t="n">
         <v>54.59000015258789</v>
@@ -2492,11 +2504,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.06482696533203</v>
+        <v>50.06482315063477</v>
       </c>
       <c r="C88" t="n">
         <v>56.79999923706055</v>
@@ -2521,7 +2533,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2550,7 +2562,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2579,11 +2591,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>55.66186141967773</v>
+        <v>55.6618537902832</v>
       </c>
       <c r="C91" t="n">
         <v>63.15000152587891</v>
@@ -2608,7 +2620,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2637,11 +2649,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.61696243286133</v>
+        <v>53.61696624755859</v>
       </c>
       <c r="C93" t="n">
         <v>60.83000183105469</v>
@@ -2666,11 +2678,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>56.84296035766602</v>
+        <v>56.84296417236328</v>
       </c>
       <c r="C94" t="n">
         <v>64.48999786376953</v>
@@ -2695,11 +2707,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>60.456787109375</v>
+        <v>60.45680618286133</v>
       </c>
       <c r="C95" t="n">
         <v>68.58999633789062</v>
@@ -2724,11 +2736,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>62.17558670043945</v>
+        <v>62.17556381225586</v>
       </c>
       <c r="C96" t="n">
         <v>70.54000091552734</v>
@@ -2753,11 +2765,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.17208099365234</v>
+        <v>68.17206573486328</v>
       </c>
       <c r="C97" t="n">
         <v>76.40000152587891</v>
@@ -2782,11 +2794,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>64.79023742675781</v>
+        <v>64.79024505615234</v>
       </c>
       <c r="C98" t="n">
         <v>72.61000061035156</v>
@@ -2811,11 +2823,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>72.10714721679688</v>
+        <v>72.10713195800781</v>
       </c>
       <c r="C99" t="n">
         <v>80.80999755859375</v>
@@ -2840,7 +2852,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2869,7 +2881,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2898,11 +2910,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>74.96251678466797</v>
+        <v>74.96250915527344</v>
       </c>
       <c r="C102" t="n">
         <v>84.01000213623047</v>
@@ -2927,11 +2939,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>76.50619506835938</v>
+        <v>76.50621032714844</v>
       </c>
       <c r="C103" t="n">
         <v>85.73999786376953</v>
@@ -2956,11 +2968,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>76.63112640380859</v>
+        <v>76.63111114501953</v>
       </c>
       <c r="C104" t="n">
         <v>85.87999725341797</v>
@@ -2985,11 +2997,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>80.20033264160156</v>
+        <v>80.20032501220703</v>
       </c>
       <c r="C105" t="n">
         <v>89.87999725341797</v>
@@ -3014,11 +3026,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>79.44189453125</v>
+        <v>79.44187927246094</v>
       </c>
       <c r="C106" t="n">
         <v>89.02999877929688</v>
@@ -3043,11 +3055,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>81.53881072998047</v>
+        <v>81.53879547119141</v>
       </c>
       <c r="C107" t="n">
         <v>91.37999725341797</v>
@@ -3072,11 +3084,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>82.54709625244141</v>
+        <v>82.547119140625</v>
       </c>
       <c r="C108" t="n">
         <v>92.51000213623047</v>
@@ -3101,7 +3113,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3130,11 +3142,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>82.19563293457031</v>
+        <v>82.19561767578125</v>
       </c>
       <c r="C110" t="n">
         <v>90.95999908447266</v>
@@ -3159,11 +3171,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>94.05146026611328</v>
+        <v>94.05148315429688</v>
       </c>
       <c r="C111" t="n">
         <v>104.0800018310547</v>
@@ -3188,11 +3200,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>94.78341674804688</v>
+        <v>94.78343963623047</v>
       </c>
       <c r="C112" t="n">
         <v>104.8899993896484</v>
@@ -3217,11 +3229,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>98.244384765625</v>
+        <v>98.24439239501953</v>
       </c>
       <c r="C113" t="n">
         <v>108.7200012207031</v>
@@ -3246,11 +3258,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>99.73539733886719</v>
+        <v>99.73538970947266</v>
       </c>
       <c r="C114" t="n">
         <v>110.370002746582</v>
@@ -3275,11 +3287,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>103.1421432495117</v>
+        <v>103.1421356201172</v>
       </c>
       <c r="C115" t="n">
         <v>114.1399993896484</v>
@@ -3304,11 +3316,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>109.0681991577148</v>
+        <v>109.0681762695312</v>
       </c>
       <c r="C116" t="n">
         <v>120</v>
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3362,11 +3374,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>92.88972473144531</v>
+        <v>92.88973236083984</v>
       </c>
       <c r="C118" t="n">
         <v>102.1999969482422</v>
@@ -3391,7 +3403,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3420,11 +3432,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>103.1330642700195</v>
+        <v>103.133056640625</v>
       </c>
       <c r="C120" t="n">
         <v>113.4700012207031</v>
@@ -3449,7 +3461,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3478,7 +3490,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3507,7 +3519,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3536,11 +3548,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>90.84161376953125</v>
+        <v>90.84162139892578</v>
       </c>
       <c r="C124" t="n">
         <v>99.30999755859375</v>
@@ -3565,7 +3577,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3594,11 +3606,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>90.75927734375</v>
+        <v>90.75928497314453</v>
       </c>
       <c r="C126" t="n">
         <v>99.22000122070312</v>
@@ -3623,11 +3635,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>89.47866821289062</v>
+        <v>89.47867584228516</v>
       </c>
       <c r="C127" t="n">
         <v>97.81999969482422</v>
@@ -3652,7 +3664,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3681,11 +3693,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>87.03285217285156</v>
+        <v>87.03282928466797</v>
       </c>
       <c r="C129" t="n">
         <v>94.45999908447266</v>
@@ -3710,11 +3722,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>85.55867004394531</v>
+        <v>85.55863952636719</v>
       </c>
       <c r="C130" t="n">
         <v>92.86000061035156</v>
@@ -3739,7 +3751,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3768,11 +3780,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>91.32644653320312</v>
+        <v>91.32645416259766</v>
       </c>
       <c r="C132" t="n">
         <v>99.12000274658203</v>
@@ -3797,11 +3809,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>96.76549530029297</v>
+        <v>96.76548767089844</v>
       </c>
       <c r="C133" t="n">
         <v>104.2200012207031</v>
@@ -3826,11 +3838,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>102.7355651855469</v>
+        <v>102.7355728149414</v>
       </c>
       <c r="C134" t="n">
         <v>110.6500015258789</v>
@@ -3855,7 +3867,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3884,11 +3896,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>105.2795791625977</v>
+        <v>105.2795867919922</v>
       </c>
       <c r="C136" t="n">
         <v>113.3899993896484</v>
@@ -3913,11 +3925,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>107.3315124511719</v>
+        <v>107.3315200805664</v>
       </c>
       <c r="C137" t="n">
         <v>115.5999984741211</v>
@@ -3942,7 +3954,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3971,11 +3983,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>98.65028381347656</v>
+        <v>98.65029144287109</v>
       </c>
       <c r="C139" t="n">
         <v>106.25</v>
@@ -4000,7 +4012,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4029,11 +4041,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>94.66048431396484</v>
+        <v>94.66049194335938</v>
       </c>
       <c r="C141" t="n">
         <v>101.1999969482422</v>
@@ -4058,7 +4070,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4087,11 +4099,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>91.48957061767578</v>
+        <v>91.48956298828125</v>
       </c>
       <c r="C143" t="n">
         <v>97.80999755859375</v>
@@ -4116,11 +4128,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>98.04656219482422</v>
+        <v>98.04656982421875</v>
       </c>
       <c r="C144" t="n">
         <v>104.8199996948242</v>
@@ -4145,11 +4157,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>101.3717269897461</v>
+        <v>101.371711730957</v>
       </c>
       <c r="C145" t="n">
         <v>107.5100021362305</v>
@@ -4174,11 +4186,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>102.4654922485352</v>
+        <v>102.4654846191406</v>
       </c>
       <c r="C146" t="n">
         <v>108.6699981689453</v>
@@ -4203,11 +4215,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>97.27008819580078</v>
+        <v>97.27008056640625</v>
       </c>
       <c r="C147" t="n">
         <v>103.1600036621094</v>
@@ -4232,7 +4244,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4261,7 +4273,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4290,11 +4302,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>93.79075622558594</v>
+        <v>93.79076385498047</v>
       </c>
       <c r="C150" t="n">
         <v>99.47000122070312</v>
@@ -4319,11 +4331,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>98.82586669921875</v>
+        <v>98.82587432861328</v>
       </c>
       <c r="C151" t="n">
         <v>104.8099975585938</v>
@@ -4348,11 +4360,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>107.9369964599609</v>
+        <v>107.93701171875</v>
       </c>
       <c r="C152" t="n">
         <v>113.5599975585938</v>
@@ -4377,11 +4389,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>106.4732437133789</v>
+        <v>106.473258972168</v>
       </c>
       <c r="C153" t="n">
         <v>112.0199966430664</v>
@@ -4406,11 +4418,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>111.1496276855469</v>
+        <v>111.1496429443359</v>
       </c>
       <c r="C154" t="n">
         <v>116.9400024414062</v>
@@ -4435,11 +4447,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>109.1441268920898</v>
+        <v>109.1441192626953</v>
       </c>
       <c r="C155" t="n">
         <v>114.8300018310547</v>
@@ -4464,11 +4476,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>109.7714538574219</v>
+        <v>109.7714309692383</v>
       </c>
       <c r="C156" t="n">
         <v>115.4899978637695</v>
@@ -4493,11 +4505,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>105.0290145874023</v>
+        <v>105.0290298461914</v>
       </c>
       <c r="C157" t="n">
         <v>109.6500015258789</v>
@@ -4522,11 +4534,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>106.8202056884766</v>
+        <v>106.8202209472656</v>
       </c>
       <c r="C158" t="n">
         <v>111.5199966430664</v>
@@ -4551,11 +4563,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>108.0845794677734</v>
+        <v>108.0845947265625</v>
       </c>
       <c r="C159" t="n">
         <v>112.8399963378906</v>
@@ -4580,7 +4592,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4609,11 +4621,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>131.1976928710938</v>
+        <v>131.1976776123047</v>
       </c>
       <c r="C161" t="n">
         <v>136.9700012207031</v>
@@ -4638,11 +4650,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>126.4754333496094</v>
+        <v>126.475456237793</v>
       </c>
       <c r="C162" t="n">
         <v>132.0399932861328</v>
@@ -4667,11 +4679,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>133.7551574707031</v>
+        <v>133.755126953125</v>
       </c>
       <c r="C163" t="n">
         <v>139.6399993896484</v>
@@ -4696,11 +4708,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>137.8314361572266</v>
+        <v>137.8314208984375</v>
       </c>
       <c r="C164" t="n">
         <v>143.0099945068359</v>
@@ -4725,11 +4737,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>132.2896575927734</v>
+        <v>132.2896728515625</v>
       </c>
       <c r="C165" t="n">
         <v>137.2599945068359</v>
@@ -4754,11 +4766,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>125.6009902954102</v>
+        <v>125.6009674072266</v>
       </c>
       <c r="C166" t="n">
         <v>130.3200073242188</v>
@@ -4783,11 +4795,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>125.2154541015625</v>
+        <v>125.215446472168</v>
       </c>
       <c r="C167" t="n">
         <v>129.9199981689453</v>
@@ -4812,7 +4824,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4841,7 +4853,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4870,11 +4882,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>134.1002960205078</v>
+        <v>134.1002807617188</v>
       </c>
       <c r="C170" t="n">
         <v>138.3099975585938</v>
@@ -4899,11 +4911,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>114.0690994262695</v>
+        <v>114.0691146850586</v>
       </c>
       <c r="C171" t="n">
         <v>117.6500015258789</v>
@@ -4928,11 +4940,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>93.65979766845703</v>
+        <v>93.65980529785156</v>
       </c>
       <c r="C172" t="n">
         <v>96.59999847412109</v>
@@ -4957,11 +4969,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>104.858268737793</v>
+        <v>104.8582534790039</v>
       </c>
       <c r="C173" t="n">
         <v>108.1500015258789</v>
@@ -4986,11 +4998,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>113.7297592163086</v>
+        <v>113.7297668457031</v>
       </c>
       <c r="C174" t="n">
         <v>117.3000030517578</v>
@@ -5015,11 +5027,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>108.1159973144531</v>
+        <v>108.1159896850586</v>
       </c>
       <c r="C175" t="n">
         <v>111.5100021362305</v>
@@ -5044,11 +5056,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>113.380729675293</v>
+        <v>113.3807144165039</v>
       </c>
       <c r="C176" t="n">
         <v>116.9400024414062</v>
@@ -5073,11 +5085,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.8562850952148</v>
+        <v>127.8562927246094</v>
       </c>
       <c r="C177" t="n">
         <v>131.8699951171875</v>
@@ -5100,11 +5112,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>120.3034057617188</v>
+        <v>120.3033981323242</v>
       </c>
       <c r="C178" t="n">
         <v>124.0800018310547</v>
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>117.5595321655273</v>
+        <v>117.5595397949219</v>
       </c>
       <c r="C179" t="n">
         <v>121.25</v>
@@ -5154,11 +5166,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>143.5050201416016</v>
+        <v>143.5050506591797</v>
       </c>
       <c r="C180" t="n">
         <v>148.0099945068359</v>
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>175.6654357910156</v>
+        <v>175.6654510498047</v>
       </c>
       <c r="C181" t="n">
         <v>181.1799926757812</v>
@@ -5208,7 +5220,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5235,7 +5247,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5262,7 +5274,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5289,7 +5301,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5316,7 +5328,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5343,11 +5355,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>170.4201202392578</v>
+        <v>170.4201507568359</v>
       </c>
       <c r="C187" t="n">
         <v>175.7700042724609</v>
@@ -5370,7 +5382,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5397,11 +5409,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>175.7818145751953</v>
+        <v>175.7817993164062</v>
       </c>
       <c r="C189" t="n">
         <v>181.3000030517578</v>
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>164.0210266113281</v>
+        <v>164.0210113525391</v>
       </c>
       <c r="C190" t="n">
         <v>169.1699981689453</v>
@@ -5455,7 +5467,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5484,11 +5496,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>140.4896850585938</v>
+        <v>140.4897155761719</v>
       </c>
       <c r="C192" t="n">
         <v>144.8999938964844</v>
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>150.1756286621094</v>
+        <v>150.1756439208984</v>
       </c>
       <c r="C193" t="n">
         <v>154.8899993896484</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>138.6184234619141</v>
+        <v>138.6184539794922</v>
       </c>
       <c r="C194" t="n">
         <v>142.9700012207031</v>
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>143.9413452148438</v>
+        <v>143.9413757324219</v>
       </c>
       <c r="C195" t="n">
         <v>148.4600067138672</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>132.9852905273438</v>
+        <v>132.9853057861328</v>
       </c>
       <c r="C196" t="n">
         <v>137.1600036621094</v>
@@ -5629,11 +5641,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>108.2323303222656</v>
+        <v>108.2323379516602</v>
       </c>
       <c r="C197" t="n">
         <v>111.629997253418</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>107.0785675048828</v>
+        <v>107.0785522460938</v>
       </c>
       <c r="C198" t="n">
         <v>110.4400024414062</v>
@@ -5687,7 +5699,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5716,7 +5728,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>108.6686401367188</v>
+        <v>108.6686477661133</v>
       </c>
       <c r="C201" t="n">
         <v>112.0800018310547</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>91.45889282226562</v>
+        <v>91.45890045166016</v>
       </c>
       <c r="C202" t="n">
         <v>94.33000183105469</v>
@@ -5803,11 +5815,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>103.2972640991211</v>
+        <v>103.297248840332</v>
       </c>
       <c r="C203" t="n">
         <v>106.5400009155273</v>
@@ -5832,7 +5844,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>84.23564910888672</v>
+        <v>84.23564147949219</v>
       </c>
       <c r="C205" t="n">
         <v>86.87999725341797</v>
@@ -5890,7 +5902,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>97.08235168457031</v>
+        <v>97.08236694335938</v>
       </c>
       <c r="C208" t="n">
         <v>100.129997253418</v>
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>99.38023376464844</v>
+        <v>99.38022613525391</v>
       </c>
       <c r="C209" t="n">
         <v>102.5</v>
@@ -6006,11 +6018,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>85.28277587890625</v>
+        <v>85.28278350830078</v>
       </c>
       <c r="C210" t="n">
         <v>87.95999908447266</v>
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,7 +6076,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6122,11 +6134,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>78.58309936523438</v>
+        <v>78.58309173583984</v>
       </c>
       <c r="C214" t="n">
         <v>81.05000305175781</v>
@@ -6151,11 +6163,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>79.10665893554688</v>
+        <v>79.10666656494141</v>
       </c>
       <c r="C215" t="n">
         <v>81.58999633789062</v>
@@ -6180,11 +6192,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>89.86882019042969</v>
+        <v>89.86881256103516</v>
       </c>
       <c r="C216" t="n">
         <v>92.69000244140625</v>
@@ -6209,7 +6221,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>93.43004608154297</v>
+        <v>93.4300537109375</v>
       </c>
       <c r="C218" t="n">
         <v>96.05000305175781</v>
@@ -6267,7 +6279,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>119.0223999023438</v>
+        <v>119.0223922729492</v>
       </c>
       <c r="C220" t="n">
         <v>122.3600006103516</v>
@@ -6325,7 +6337,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>101.0756530761719</v>
+        <v>101.0756607055664</v>
       </c>
       <c r="C222" t="n">
         <v>103.9100036621094</v>
@@ -6383,7 +6395,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6412,11 +6424,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>91.55487823486328</v>
+        <v>91.55487060546875</v>
       </c>
       <c r="C224" t="n">
         <v>93.69000244140625</v>
@@ -6441,7 +6453,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6470,7 +6482,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6499,7 +6511,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6528,7 +6540,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6557,7 +6569,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6586,11 +6598,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>110.9730072021484</v>
+        <v>110.9729995727539</v>
       </c>
       <c r="C230" t="n">
         <v>113.0599975585938</v>
@@ -6615,7 +6627,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6644,7 +6656,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6673,11 +6685,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>89.27114105224609</v>
+        <v>89.27113342285156</v>
       </c>
       <c r="C233" t="n">
         <v>90.94999694824219</v>
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6760,11 +6772,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>117.4098892211914</v>
+        <v>117.4098815917969</v>
       </c>
       <c r="C236" t="n">
         <v>119.1100006103516</v>
@@ -6789,7 +6801,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,11 +6859,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>111.0125198364258</v>
+        <v>111.0125274658203</v>
       </c>
       <c r="C239" t="n">
         <v>112.620002746582</v>
@@ -6876,11 +6888,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>102.9788436889648</v>
+        <v>102.9788513183594</v>
       </c>
       <c r="C240" t="n">
         <v>104.4700012207031</v>
@@ -6905,7 +6917,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6963,7 +6975,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,7 +7062,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7166,32 +7178,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>103.4599990844727</v>
+        <v>105.5599975585938</v>
       </c>
       <c r="C250" t="n">
-        <v>103.4599990844727</v>
+        <v>105.5599975585938</v>
       </c>
       <c r="D250" t="n">
-        <v>132020600</v>
+        <v>139904800</v>
       </c>
       <c r="E250" t="n">
         <v>4.84</v>
       </c>
       <c r="F250" t="n">
-        <v>21.3760328686927</v>
+        <v>21.80991685094912</v>
       </c>
       <c r="G250" t="n">
         <v>1726686902</v>
       </c>
       <c r="H250" t="n">
-        <v>178643025300.0909</v>
+        <v>182269065159.5758</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07645891090450861</v>
+        <v>0.08102499638929907</v>
       </c>
     </row>
   </sheetData>
@@ -7223,75 +7235,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39537</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39719</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39809</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39810</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39900</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40309</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39901</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39992</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40089</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7486,7 +7498,7 @@
       <c r="I6" t="n">
         <v>1.76</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K6" t="n">
@@ -7499,13 +7511,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40090</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40180</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7532,7 +7544,7 @@
       <c r="I7" t="n">
         <v>1.75</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K7" t="n">
@@ -7545,13 +7557,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40181</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40271</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40309</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7578,7 +7590,7 @@
       <c r="I8" t="n">
         <v>1.9</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K8" t="n">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40272</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40362</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40400</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7624,7 +7636,7 @@
       <c r="I9" t="n">
         <v>2.06</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K9" t="n">
@@ -7637,13 +7649,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40363</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40453</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7670,7 +7682,7 @@
       <c r="I10" t="n">
         <v>2.02</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K10" t="n">
@@ -7683,13 +7695,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40454</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7716,7 +7728,7 @@
       <c r="I11" t="n">
         <v>2.26</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="K11" t="n">
@@ -7729,13 +7741,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40545</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="I12" t="n">
         <v>2.27</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K12" t="n">
@@ -7775,13 +7787,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40636</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7808,7 +7820,7 @@
       <c r="I13" t="n">
         <v>2.37</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="K13" t="n">
@@ -7821,13 +7833,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40727</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7854,7 +7866,7 @@
       <c r="I14" t="n">
         <v>2.52</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="K14" t="n">
@@ -7867,13 +7879,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40818</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7900,7 +7912,7 @@
       <c r="I15" t="n">
         <v>2.64</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="K15" t="n">
@@ -7913,13 +7925,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="I16" t="n">
         <v>2.78</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K16" t="n">
@@ -7959,13 +7971,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7992,7 +8004,7 @@
       <c r="I17" t="n">
         <v>3.02</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K17" t="n">
@@ -8005,13 +8017,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8038,7 +8050,7 @@
       <c r="I18" t="n">
         <v>3.12</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="K18" t="n">
@@ -8051,13 +8063,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8084,7 +8096,7 @@
       <c r="I19" t="n">
         <v>3.09</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="K19" t="n">
@@ -8097,13 +8109,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8130,7 +8142,7 @@
       <c r="I20" t="n">
         <v>3.29</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -8143,13 +8155,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8176,7 +8188,7 @@
       <c r="I21" t="n">
         <v>3.29</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K21" t="n">
@@ -8189,13 +8201,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41598</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="I22" t="n">
         <v>3.38</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41598</v>
       </c>
       <c r="K22" t="n">
@@ -8235,13 +8247,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8268,7 +8280,7 @@
       <c r="I23" t="n">
         <v>3.64</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="K23" t="n">
@@ -8281,13 +8293,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41637</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8314,7 +8326,7 @@
       <c r="I24" t="n">
         <v>3.89</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K24" t="n">
@@ -8327,13 +8339,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8360,7 +8372,7 @@
       <c r="I25" t="n">
         <v>4.16</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K25" t="n">
@@ -8373,13 +8385,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8406,7 +8418,7 @@
       <c r="I26" t="n">
         <v>4.25</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="K26" t="n">
@@ -8419,13 +8431,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8452,7 +8464,7 @@
       <c r="I27" t="n">
         <v>4.49</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="K27" t="n">
@@ -8465,13 +8477,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42001</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42091</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8498,7 +8510,7 @@
       <c r="I28" t="n">
         <v>4.640000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K28" t="n">
@@ -8511,13 +8523,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42182</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8544,7 +8556,7 @@
       <c r="I29" t="n">
         <v>4.81</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K29" t="n">
@@ -8557,13 +8569,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42280</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8590,7 +8602,7 @@
       <c r="I30" t="n">
         <v>4.9</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="K30" t="n">
@@ -8603,13 +8615,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42281</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42371</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8636,7 +8648,7 @@
       <c r="I31" t="n">
         <v>5.359999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="K31" t="n">
@@ -8649,13 +8661,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42372</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42462</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8682,7 +8694,7 @@
       <c r="I32" t="n">
         <v>5.43</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="K32" t="n">
@@ -8695,13 +8707,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42553</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8728,7 +8740,7 @@
       <c r="I33" t="n">
         <v>5.57</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="K33" t="n">
@@ -8741,13 +8753,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8774,7 +8786,7 @@
       <c r="I34" t="n">
         <v>5.720000000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="K34" t="n">
@@ -8787,13 +8799,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8820,7 +8832,7 @@
       <c r="I35" t="n">
         <v>5.54</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="K35" t="n">
@@ -8833,13 +8845,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8866,7 +8878,7 @@
       <c r="I36" t="n">
         <v>5.74</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="K36" t="n">
@@ -8879,13 +8891,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8912,7 +8924,7 @@
       <c r="I37" t="n">
         <v>5.66</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K37" t="n">
@@ -8925,13 +8937,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8958,7 +8970,7 @@
       <c r="I38" t="n">
         <v>5.69</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="K38" t="n">
@@ -8971,13 +8983,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9004,7 +9016,7 @@
       <c r="I39" t="n">
         <v>7.050000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="K39" t="n">
@@ -9017,13 +9029,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9050,7 +9062,7 @@
       <c r="I40" t="n">
         <v>7.5</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K40" t="n">
@@ -9063,13 +9075,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9096,7 +9108,7 @@
       <c r="I41" t="n">
         <v>7.94</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="K41" t="n">
@@ -9109,13 +9121,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="I42" t="n">
         <v>8.360000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="K42" t="n">
@@ -9155,13 +9167,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9188,7 +9200,7 @@
       <c r="I43" t="n">
         <v>7.31</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K43" t="n">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43464</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I44" t="n">
         <v>8.91</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I45" t="n">
         <v>7.93</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K45" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43789</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I46" t="n">
         <v>6.96</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43789</v>
       </c>
       <c r="K46" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43737</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43827</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I47" t="n">
         <v>6.26</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="K47" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43828</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I48" t="n">
         <v>2.96</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K48" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43919</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I49" t="n">
         <v>-0.6199999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K49" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44010</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44107</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I50" t="n">
         <v>-1.59</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="K50" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44108</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44198</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I51" t="n">
         <v>-2.74</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K51" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44199</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44289</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I52" t="n">
         <v>-2.5</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="K52" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44290</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44380</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I53" t="n">
         <v>0.61</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="K53" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44381</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44471</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I54" t="n">
         <v>1.09</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="K54" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44472</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I55" t="n">
         <v>1.68</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K55" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44563</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I56" t="n">
         <v>1.45</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="K56" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44654</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I57" t="n">
         <v>1.72</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="K57" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44745</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I58" t="n">
         <v>1.72</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="K58" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44836</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I59" t="n">
         <v>1.82</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="K59" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I60" t="n">
         <v>2.25</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="K60" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45018</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I61" t="n">
         <v>1.23</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="K61" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45109</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I62" t="n">
         <v>1.29</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="K62" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I63" t="n">
         <v>1.63</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="K63" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I64" t="n">
         <v>0.9300000000000004</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K64" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I65" t="n">
         <v>2.61</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K65" t="n">
@@ -10213,13 +10225,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10246,7 +10258,7 @@
       <c r="I66" t="n">
         <v>2.72</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="K66" t="n">
@@ -10259,13 +10271,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45564</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10292,7 +10304,7 @@
       <c r="I67" t="n">
         <v>3.08</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K67" t="n">
@@ -10305,13 +10317,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45655</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10338,7 +10350,7 @@
       <c r="I68" t="n">
         <v>4.9</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10351,13 +10363,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45746</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10384,7 +10396,7 @@
       <c r="I69" t="n">
         <v>6.390000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K69" t="n">
@@ -10397,13 +10409,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45837</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10430,7 +10442,7 @@
       <c r="I70" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="K70" t="n">
@@ -10443,13 +10455,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10476,7 +10488,7 @@
       <c r="I71" t="n">
         <v>6.79</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="K71" t="n">
@@ -10489,13 +10501,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46019</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="I72" t="n">
         <v>6.250000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10535,13 +10547,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46110</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46200</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10568,7 +10580,7 @@
       <c r="I73" t="n">
         <v>4.84</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K73" t="n">
@@ -10605,52 +10617,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40021</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="C2" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40137</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40149</v>
       </c>
       <c r="C3" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40214</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="C4" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40302</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40309</v>
       </c>
       <c r="C5" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40393</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40400</v>
       </c>
       <c r="C6" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40498</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="C7" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="C8" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40666</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C9" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40757</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C10" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40862</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="C11" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="C12" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C14" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41227</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="C15" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41304</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41310</v>
       </c>
       <c r="C16" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41592</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41598</v>
       </c>
       <c r="C19" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41668</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="C20" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C21" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41850</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41956</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41962</v>
       </c>
       <c r="C23" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42032</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42038</v>
       </c>
       <c r="C24" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42123</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C25" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42214</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42326</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="C27" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42403</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="C28" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42494</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="C29" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42585</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="C30" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42690</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="C31" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="C32" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42858</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="C33" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42949</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C34" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43054</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="C35" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="C36" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43222</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C37" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43319</v>
       </c>
       <c r="C38" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43418</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="C39" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43495</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="C40" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C41" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43782</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43789</v>
       </c>
       <c r="C43" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43859</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="C44" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43950</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44153</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="C47" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44230</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C48" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44321</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44329</v>
       </c>
       <c r="C49" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44412</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="C50" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44517</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="C51" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44594</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C52" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44685</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44692</v>
       </c>
       <c r="C53" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44776</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44783</v>
       </c>
       <c r="C54" t="n">
@@ -12343,10 +12355,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44888</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="C55" t="n">
@@ -12375,10 +12387,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44944</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="C56" t="n">
@@ -12407,10 +12419,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="C57" t="n">
@@ -12439,10 +12451,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45049</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="C58" t="n">
@@ -12471,10 +12483,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45140</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="C59" t="n">
@@ -12503,10 +12515,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45245</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="C60" t="n">
@@ -12535,10 +12547,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45308</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45315</v>
       </c>
       <c r="C61" t="n">
@@ -12567,10 +12579,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="C62" t="n">
@@ -12599,10 +12611,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C63" t="n">
@@ -12631,10 +12643,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C64" t="n">
@@ -12663,10 +12675,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45602</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45610</v>
       </c>
       <c r="C65" t="n">
@@ -12695,10 +12707,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45686</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C66" t="n">
@@ -12727,10 +12739,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C67" t="n">
@@ -12759,10 +12771,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C68" t="n">
@@ -12791,10 +12803,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45966</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45974</v>
       </c>
       <c r="C69" t="n">
@@ -12823,10 +12835,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="C70" t="n">
@@ -12855,10 +12867,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C71" t="n">
@@ -12887,10 +12899,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46232</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C72" t="n">
@@ -12937,12 +12949,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/DIS.xlsx
+++ b/salidas/empresas/DIS.xlsx
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>22.18869781494141</v>
+        <v>22.18869972229004</v>
       </c>
       <c r="C4" t="n">
         <v>27.51348495483398</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>22.2443904876709</v>
+        <v>22.244384765625</v>
       </c>
       <c r="C5" t="n">
         <v>27.58254051208496</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>23.86736679077148</v>
+        <v>23.86736488342285</v>
       </c>
       <c r="C7" t="n">
         <v>29.59499931335449</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.58891868591309</v>
+        <v>23.58891677856445</v>
       </c>
       <c r="C9" t="n">
         <v>29.24972534179688</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>24.59134674072266</v>
+        <v>24.59134483337402</v>
       </c>
       <c r="C10" t="n">
         <v>30.49271583557129</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>25.02891540527344</v>
+        <v>25.0289134979248</v>
       </c>
       <c r="C11" t="n">
         <v>31.0352897644043</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>26.29388046264648</v>
+        <v>26.29388427734375</v>
       </c>
       <c r="C12" t="n">
         <v>32.60382461547852</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>27.51141166687012</v>
+        <v>27.51140975952148</v>
       </c>
       <c r="C13" t="n">
         <v>33.80735397338867</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>27.49534797668457</v>
+        <v>27.49534606933594</v>
       </c>
       <c r="C15" t="n">
         <v>33.78762435913086</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>28.08138465881348</v>
+        <v>28.08139038085938</v>
       </c>
       <c r="C17" t="n">
         <v>34.50777053833008</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.4506721496582</v>
+        <v>28.45066833496094</v>
       </c>
       <c r="C18" t="n">
         <v>34.9615592956543</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>27.78210067749023</v>
+        <v>27.78210258483887</v>
       </c>
       <c r="C19" t="n">
         <v>34.13999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>26.85440063476562</v>
+        <v>26.85440254211426</v>
       </c>
       <c r="C20" t="n">
         <v>33</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>27.34267044067383</v>
+        <v>27.3426685333252</v>
       </c>
       <c r="C21" t="n">
         <v>33.59999847412109</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>27.98554801940918</v>
+        <v>27.98555183410645</v>
       </c>
       <c r="C22" t="n">
         <v>34.38999938964844</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.18084716796875</v>
+        <v>28.18085098266602</v>
       </c>
       <c r="C23" t="n">
         <v>34.63000106811523</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>26.55225372314453</v>
+        <v>26.55225563049316</v>
       </c>
       <c r="C25" t="n">
         <v>32.27999877929688</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.54520606994629</v>
+        <v>24.54520988464355</v>
       </c>
       <c r="C26" t="n">
         <v>29.84000015258789</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.67563819885254</v>
+        <v>26.6756420135498</v>
       </c>
       <c r="C29" t="n">
         <v>32.43000030517578</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.66389083862305</v>
+        <v>25.66389465332031</v>
       </c>
       <c r="C31" t="n">
         <v>31.20000076293945</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>24.96471405029297</v>
+        <v>24.96471977233887</v>
       </c>
       <c r="C32" t="n">
         <v>30.35000038146973</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.60983657836914</v>
+        <v>26.60983467102051</v>
       </c>
       <c r="C33" t="n">
         <v>32.34999847412109</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.31254196166992</v>
+        <v>21.31254768371582</v>
       </c>
       <c r="C35" t="n">
         <v>25.90999984741211</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>18.52407073974609</v>
+        <v>18.5240650177002</v>
       </c>
       <c r="C36" t="n">
         <v>22.52000045776367</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.94365692138672</v>
+        <v>18.94366645812988</v>
       </c>
       <c r="C37" t="n">
         <v>22.69000053405762</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.26552963256836</v>
+        <v>17.26553153991699</v>
       </c>
       <c r="C38" t="n">
         <v>20.68000030517578</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.00110816955566</v>
+        <v>14.00111198425293</v>
       </c>
       <c r="C39" t="n">
         <v>16.77000045776367</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.1616039276123</v>
+        <v>15.16161155700684</v>
       </c>
       <c r="C40" t="n">
         <v>18.15999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.28409385681152</v>
+        <v>18.28409767150879</v>
       </c>
       <c r="C41" t="n">
         <v>21.89999961853027</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>20.97243690490723</v>
+        <v>20.97244071960449</v>
       </c>
       <c r="C44" t="n">
         <v>25.1200008392334</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>21.74053955078125</v>
+        <v>21.74054336547852</v>
       </c>
       <c r="C45" t="n">
         <v>26.04000091552734</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>22.85094261169434</v>
+        <v>22.85094451904297</v>
       </c>
       <c r="C47" t="n">
         <v>27.3700008392334</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.48213195800781</v>
+        <v>29.48213577270508</v>
       </c>
       <c r="C52" t="n">
         <v>34.90999984741211</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.1120491027832</v>
+        <v>31.11205863952637</v>
       </c>
       <c r="C53" t="n">
         <v>36.84000015258789</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.22380065917969</v>
+        <v>28.22379875183105</v>
       </c>
       <c r="C54" t="n">
         <v>33.41999816894531</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>26.60232925415039</v>
+        <v>26.60232734680176</v>
       </c>
       <c r="C55" t="n">
         <v>31.5</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>28.45182228088379</v>
+        <v>28.45181846618652</v>
       </c>
       <c r="C56" t="n">
         <v>33.68999862670898</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.95355606079102</v>
+        <v>27.95355415344238</v>
       </c>
       <c r="C58" t="n">
         <v>33.09999847412109</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.51244354248047</v>
+        <v>30.51244926452637</v>
       </c>
       <c r="C59" t="n">
         <v>36.13000106811523</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.8333625793457</v>
+        <v>30.83335876464844</v>
       </c>
       <c r="C60" t="n">
         <v>36.5099983215332</v>
@@ -1754,7 +1754,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>33.18547058105469</v>
+        <v>33.18548202514648</v>
       </c>
       <c r="C62" t="n">
         <v>38.86999893188477</v>
@@ -1783,7 +1783,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>37.34326553344727</v>
+        <v>37.34326171875</v>
       </c>
       <c r="C63" t="n">
         <v>43.7400016784668</v>
@@ -1899,7 +1899,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>33.33061981201172</v>
+        <v>33.33061218261719</v>
       </c>
       <c r="C67" t="n">
         <v>39.04000091552734</v>
@@ -1928,7 +1928,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>32.97203063964844</v>
+        <v>32.9720344543457</v>
       </c>
       <c r="C68" t="n">
         <v>38.61999893188477</v>
@@ -1957,7 +1957,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>29.07891464233398</v>
+        <v>29.07891845703125</v>
       </c>
       <c r="C69" t="n">
         <v>34.06000137329102</v>
@@ -2015,7 +2015,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>29.77899551391602</v>
+        <v>29.77899742126465</v>
       </c>
       <c r="C71" t="n">
         <v>34.88000106811523</v>
@@ -2044,7 +2044,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>30.60713958740234</v>
+        <v>30.60714149475098</v>
       </c>
       <c r="C72" t="n">
         <v>35.84999847412109</v>
@@ -2073,7 +2073,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.55346298217773</v>
+        <v>32.55345916748047</v>
       </c>
       <c r="C73" t="n">
         <v>37.5</v>
@@ -2102,7 +2102,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>33.76879501342773</v>
+        <v>33.7687873840332</v>
       </c>
       <c r="C74" t="n">
         <v>38.90000152587891</v>
@@ -2131,7 +2131,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>36.45119094848633</v>
+        <v>36.45119857788086</v>
       </c>
       <c r="C75" t="n">
         <v>41.9900016784668</v>
@@ -2160,7 +2160,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>38.00507736206055</v>
+        <v>38.00508117675781</v>
       </c>
       <c r="C76" t="n">
         <v>43.77999877929688</v>
@@ -2189,7 +2189,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>37.42345809936523</v>
+        <v>37.42346572875977</v>
       </c>
       <c r="C77" t="n">
         <v>43.11000061035156</v>
@@ -2218,7 +2218,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>39.68049240112305</v>
+        <v>39.68049621582031</v>
       </c>
       <c r="C78" t="n">
         <v>45.70999908447266</v>
@@ -2247,7 +2247,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>42.10247802734375</v>
+        <v>42.10247421264648</v>
       </c>
       <c r="C79" t="n">
         <v>48.5</v>
@@ -2334,7 +2334,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>45.38386917114258</v>
+        <v>45.38386535644531</v>
       </c>
       <c r="C82" t="n">
         <v>52.27999877929688</v>
@@ -2363,7 +2363,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>42.64068603515625</v>
+        <v>42.64069747924805</v>
       </c>
       <c r="C83" t="n">
         <v>49.11999893188477</v>
@@ -2421,7 +2421,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>43.88604736328125</v>
+        <v>43.88604354858398</v>
       </c>
       <c r="C85" t="n">
         <v>49.79000091552734</v>
@@ -2450,7 +2450,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>47.49107360839844</v>
+        <v>47.49106979370117</v>
       </c>
       <c r="C86" t="n">
         <v>53.88000106811523</v>
@@ -2508,7 +2508,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.06482315063477</v>
+        <v>50.0648193359375</v>
       </c>
       <c r="C88" t="n">
         <v>56.79999923706055</v>
@@ -2566,7 +2566,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>55.60016632080078</v>
+        <v>55.60016250610352</v>
       </c>
       <c r="C90" t="n">
         <v>63.08000183105469</v>
@@ -2653,7 +2653,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>53.61696624755859</v>
+        <v>53.61696243286133</v>
       </c>
       <c r="C93" t="n">
         <v>60.83000183105469</v>
@@ -2711,7 +2711,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>60.45680618286133</v>
+        <v>60.45679473876953</v>
       </c>
       <c r="C95" t="n">
         <v>68.58999633789062</v>
@@ -2740,7 +2740,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>62.17556381225586</v>
+        <v>62.17558670043945</v>
       </c>
       <c r="C96" t="n">
         <v>70.54000091552734</v>
@@ -2769,7 +2769,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.17206573486328</v>
+        <v>68.17208099365234</v>
       </c>
       <c r="C97" t="n">
         <v>76.40000152587891</v>
@@ -2827,7 +2827,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>72.10713195800781</v>
+        <v>72.10712432861328</v>
       </c>
       <c r="C99" t="n">
         <v>80.80999755859375</v>
@@ -2856,7 +2856,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>71.44683074951172</v>
+        <v>71.44683837890625</v>
       </c>
       <c r="C100" t="n">
         <v>80.06999969482422</v>
@@ -2885,7 +2885,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>70.79544830322266</v>
+        <v>70.79546356201172</v>
       </c>
       <c r="C101" t="n">
         <v>79.33999633789062</v>
@@ -2914,7 +2914,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>74.96250915527344</v>
+        <v>74.96251678466797</v>
       </c>
       <c r="C102" t="n">
         <v>84.01000213623047</v>
@@ -2943,7 +2943,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>76.50621032714844</v>
+        <v>76.50619506835938</v>
       </c>
       <c r="C103" t="n">
         <v>85.73999786376953</v>
@@ -2972,7 +2972,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>76.63111114501953</v>
+        <v>76.63112640380859</v>
       </c>
       <c r="C104" t="n">
         <v>85.87999725341797</v>
@@ -3001,7 +3001,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>80.20032501220703</v>
+        <v>80.20034027099609</v>
       </c>
       <c r="C105" t="n">
         <v>89.87999725341797</v>
@@ -3030,7 +3030,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>79.44187927246094</v>
+        <v>79.44189453125</v>
       </c>
       <c r="C106" t="n">
         <v>89.02999877929688</v>
@@ -3059,7 +3059,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>81.53879547119141</v>
+        <v>81.53878784179688</v>
       </c>
       <c r="C107" t="n">
         <v>91.37999725341797</v>
@@ -3088,7 +3088,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>82.547119140625</v>
+        <v>82.54710388183594</v>
       </c>
       <c r="C108" t="n">
         <v>92.51000213623047</v>
@@ -3117,7 +3117,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>85.11439514160156</v>
+        <v>85.11440277099609</v>
       </c>
       <c r="C109" t="n">
         <v>94.19000244140625</v>
@@ -3146,7 +3146,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>82.19561767578125</v>
+        <v>82.19562530517578</v>
       </c>
       <c r="C110" t="n">
         <v>90.95999908447266</v>
@@ -3204,7 +3204,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>94.78343963623047</v>
+        <v>94.78341674804688</v>
       </c>
       <c r="C112" t="n">
         <v>104.8899993896484</v>
@@ -3262,7 +3262,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>99.73538970947266</v>
+        <v>99.73538208007812</v>
       </c>
       <c r="C114" t="n">
         <v>110.370002746582</v>
@@ -3349,7 +3349,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>92.598876953125</v>
+        <v>92.59888458251953</v>
       </c>
       <c r="C117" t="n">
         <v>101.879997253418</v>
@@ -3378,7 +3378,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>92.88973236083984</v>
+        <v>92.88972473144531</v>
       </c>
       <c r="C118" t="n">
         <v>102.1999969482422</v>
@@ -3407,7 +3407,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>103.3784561157227</v>
+        <v>103.3784484863281</v>
       </c>
       <c r="C119" t="n">
         <v>113.7399978637695</v>
@@ -3436,7 +3436,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>103.133056640625</v>
+        <v>103.1330413818359</v>
       </c>
       <c r="C120" t="n">
         <v>113.4700012207031</v>
@@ -3523,7 +3523,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>87.37479400634766</v>
+        <v>87.37478637695312</v>
       </c>
       <c r="C123" t="n">
         <v>95.51999664306641</v>
@@ -3552,7 +3552,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>90.84162139892578</v>
+        <v>90.84163665771484</v>
       </c>
       <c r="C124" t="n">
         <v>99.30999755859375</v>
@@ -3581,7 +3581,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>94.45479583740234</v>
+        <v>94.45478820800781</v>
       </c>
       <c r="C125" t="n">
         <v>103.2600021362305</v>
@@ -3610,7 +3610,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>90.75928497314453</v>
+        <v>90.75929260253906</v>
       </c>
       <c r="C126" t="n">
         <v>99.22000122070312</v>
@@ -3639,7 +3639,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>89.47867584228516</v>
+        <v>89.47866821289062</v>
       </c>
       <c r="C127" t="n">
         <v>97.81999969482422</v>
@@ -3668,7 +3668,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>88.40569305419922</v>
+        <v>88.40568542480469</v>
       </c>
       <c r="C128" t="n">
         <v>95.94999694824219</v>
@@ -3697,7 +3697,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>87.03282928466797</v>
+        <v>87.03285217285156</v>
       </c>
       <c r="C129" t="n">
         <v>94.45999908447266</v>
@@ -3726,7 +3726,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>85.55863952636719</v>
+        <v>85.55865478515625</v>
       </c>
       <c r="C130" t="n">
         <v>92.86000061035156</v>
@@ -3755,7 +3755,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>85.40202331542969</v>
+        <v>85.40201568603516</v>
       </c>
       <c r="C131" t="n">
         <v>92.69000244140625</v>
@@ -3813,7 +3813,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>96.76548767089844</v>
+        <v>96.76549530029297</v>
       </c>
       <c r="C133" t="n">
         <v>104.2200012207031</v>
@@ -3842,7 +3842,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>102.7355728149414</v>
+        <v>102.7355804443359</v>
       </c>
       <c r="C134" t="n">
         <v>110.6500015258789</v>
@@ -3871,7 +3871,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>102.2156219482422</v>
+        <v>102.2156372070312</v>
       </c>
       <c r="C135" t="n">
         <v>110.0899963378906</v>
@@ -3929,7 +3929,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>107.3315200805664</v>
+        <v>107.3315048217773</v>
       </c>
       <c r="C137" t="n">
         <v>115.5999984741211</v>
@@ -3958,7 +3958,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>100.2194137573242</v>
+        <v>100.2194061279297</v>
       </c>
       <c r="C138" t="n">
         <v>107.9400024414062</v>
@@ -4016,7 +4016,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>102.8263778686523</v>
+        <v>102.8263626098633</v>
       </c>
       <c r="C140" t="n">
         <v>109.9300003051758</v>
@@ -4045,7 +4045,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>94.66049194335938</v>
+        <v>94.66049957275391</v>
       </c>
       <c r="C141" t="n">
         <v>101.1999969482422</v>
@@ -4074,7 +4074,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>92.200439453125</v>
+        <v>92.20044708251953</v>
       </c>
       <c r="C142" t="n">
         <v>98.56999969482422</v>
@@ -4190,7 +4190,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>102.4654846191406</v>
+        <v>102.4654769897461</v>
       </c>
       <c r="C146" t="n">
         <v>108.6699981689453</v>
@@ -4219,7 +4219,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>97.27008056640625</v>
+        <v>97.27009582519531</v>
       </c>
       <c r="C147" t="n">
         <v>103.1600036621094</v>
@@ -4248,7 +4248,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>94.70536804199219</v>
+        <v>94.70537567138672</v>
       </c>
       <c r="C148" t="n">
         <v>100.4400024414062</v>
@@ -4335,7 +4335,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>98.82587432861328</v>
+        <v>98.82586669921875</v>
       </c>
       <c r="C151" t="n">
         <v>104.8099975585938</v>
@@ -4364,7 +4364,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>107.93701171875</v>
+        <v>107.9369964599609</v>
       </c>
       <c r="C152" t="n">
         <v>113.5599975585938</v>
@@ -4393,7 +4393,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>106.473258972168</v>
+        <v>106.4732437133789</v>
       </c>
       <c r="C153" t="n">
         <v>112.0199966430664</v>
@@ -4480,7 +4480,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>109.7714309692383</v>
+        <v>109.7714385986328</v>
       </c>
       <c r="C156" t="n">
         <v>115.4899978637695</v>
@@ -4509,7 +4509,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>105.0290298461914</v>
+        <v>105.0290145874023</v>
       </c>
       <c r="C157" t="n">
         <v>109.6500015258789</v>
@@ -4538,7 +4538,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>106.8202209472656</v>
+        <v>106.8202133178711</v>
       </c>
       <c r="C158" t="n">
         <v>111.5199966430664</v>
@@ -4567,7 +4567,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>108.0845947265625</v>
+        <v>108.0845794677734</v>
       </c>
       <c r="C159" t="n">
         <v>112.8399963378906</v>
@@ -4654,7 +4654,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>126.475456237793</v>
+        <v>126.4754333496094</v>
       </c>
       <c r="C162" t="n">
         <v>132.0399932861328</v>
@@ -4683,7 +4683,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>133.755126953125</v>
+        <v>133.7551574707031</v>
       </c>
       <c r="C163" t="n">
         <v>139.6399993896484</v>
@@ -4712,7 +4712,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>137.8314208984375</v>
+        <v>137.8314361572266</v>
       </c>
       <c r="C164" t="n">
         <v>143.0099945068359</v>
@@ -4741,7 +4741,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>132.2896728515625</v>
+        <v>132.2896575927734</v>
       </c>
       <c r="C165" t="n">
         <v>137.2599945068359</v>
@@ -4770,7 +4770,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>125.6009674072266</v>
+        <v>125.6009826660156</v>
       </c>
       <c r="C166" t="n">
         <v>130.3200073242188</v>
@@ -4799,7 +4799,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>125.215446472168</v>
+        <v>125.2154541015625</v>
       </c>
       <c r="C167" t="n">
         <v>129.9199981689453</v>
@@ -4828,7 +4828,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>146.0911254882812</v>
+        <v>146.0910949707031</v>
       </c>
       <c r="C168" t="n">
         <v>151.5800018310547</v>
@@ -4857,7 +4857,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>140.2279357910156</v>
+        <v>140.2279205322266</v>
       </c>
       <c r="C169" t="n">
         <v>144.6300048828125</v>
@@ -4944,7 +4944,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>93.65980529785156</v>
+        <v>93.65979766845703</v>
       </c>
       <c r="C172" t="n">
         <v>96.59999847412109</v>
@@ -4973,7 +4973,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>104.8582534790039</v>
+        <v>104.8582611083984</v>
       </c>
       <c r="C173" t="n">
         <v>108.1500015258789</v>
@@ -5031,7 +5031,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>108.1159896850586</v>
+        <v>108.1159973144531</v>
       </c>
       <c r="C175" t="n">
         <v>111.5100021362305</v>
@@ -5089,7 +5089,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.8562927246094</v>
+        <v>127.8562850952148</v>
       </c>
       <c r="C177" t="n">
         <v>131.8699951171875</v>
@@ -5116,7 +5116,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>120.3033981323242</v>
+        <v>120.3034133911133</v>
       </c>
       <c r="C178" t="n">
         <v>124.0800018310547</v>
@@ -5143,7 +5143,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>117.5595397949219</v>
+        <v>117.5595474243164</v>
       </c>
       <c r="C179" t="n">
         <v>121.25</v>
@@ -5197,7 +5197,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>175.6654510498047</v>
+        <v>175.6654357910156</v>
       </c>
       <c r="C181" t="n">
         <v>181.1799926757812</v>
@@ -5305,7 +5305,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>180.3581390380859</v>
+        <v>180.358154296875</v>
       </c>
       <c r="C185" t="n">
         <v>186.0200042724609</v>
@@ -5359,7 +5359,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>170.4201507568359</v>
+        <v>170.4201202392578</v>
       </c>
       <c r="C187" t="n">
         <v>175.7700042724609</v>
@@ -5442,7 +5442,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>164.0210113525391</v>
+        <v>164.0209808349609</v>
       </c>
       <c r="C190" t="n">
         <v>169.1699981689453</v>
@@ -5471,7 +5471,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>163.9240570068359</v>
+        <v>163.924072265625</v>
       </c>
       <c r="C191" t="n">
         <v>169.0700073242188</v>
@@ -5500,7 +5500,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>140.4897155761719</v>
+        <v>140.4896850585938</v>
       </c>
       <c r="C192" t="n">
         <v>144.8999938964844</v>
@@ -5558,7 +5558,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>138.6184539794922</v>
+        <v>138.6184387207031</v>
       </c>
       <c r="C194" t="n">
         <v>142.9700012207031</v>
@@ -5587,7 +5587,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>143.9413757324219</v>
+        <v>143.9413299560547</v>
       </c>
       <c r="C195" t="n">
         <v>148.4600067138672</v>
@@ -5674,7 +5674,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>107.0785522460938</v>
+        <v>107.0785598754883</v>
       </c>
       <c r="C198" t="n">
         <v>110.4400024414062</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>91.52676391601562</v>
+        <v>91.52677154541016</v>
       </c>
       <c r="C199" t="n">
         <v>94.40000152587891</v>
@@ -5732,7 +5732,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>102.8706512451172</v>
+        <v>102.8706436157227</v>
       </c>
       <c r="C200" t="n">
         <v>106.0999984741211</v>
@@ -5761,7 +5761,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>108.6686477661133</v>
+        <v>108.6686325073242</v>
       </c>
       <c r="C201" t="n">
         <v>112.0800018310547</v>
@@ -5819,7 +5819,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>103.297248840332</v>
+        <v>103.2972564697266</v>
       </c>
       <c r="C203" t="n">
         <v>106.5400009155273</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>94.89115142822266</v>
+        <v>94.89114379882812</v>
       </c>
       <c r="C204" t="n">
         <v>97.87000274658203</v>
@@ -5877,7 +5877,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>84.23564147949219</v>
+        <v>84.23564910888672</v>
       </c>
       <c r="C205" t="n">
         <v>86.87999725341797</v>
@@ -5906,7 +5906,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>105.1879043579102</v>
+        <v>105.1879119873047</v>
       </c>
       <c r="C206" t="n">
         <v>108.4899978637695</v>
@@ -5935,7 +5935,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>96.57819366455078</v>
+        <v>96.57818603515625</v>
       </c>
       <c r="C207" t="n">
         <v>99.61000061035156</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>97.08236694335938</v>
+        <v>97.08235931396484</v>
       </c>
       <c r="C208" t="n">
         <v>100.129997253418</v>
@@ -6022,7 +6022,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>85.28278350830078</v>
+        <v>85.28277587890625</v>
       </c>
       <c r="C210" t="n">
         <v>87.95999908447266</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>86.18447113037109</v>
+        <v>86.18446350097656</v>
       </c>
       <c r="C212" t="n">
         <v>88.88999938964844</v>
@@ -6109,7 +6109,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>81.13304901123047</v>
+        <v>81.13304138183594</v>
       </c>
       <c r="C213" t="n">
         <v>83.68000030517578</v>
@@ -6167,7 +6167,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>79.10666656494141</v>
+        <v>79.10665893554688</v>
       </c>
       <c r="C215" t="n">
         <v>81.58999633789062</v>
@@ -6196,7 +6196,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>89.86881256103516</v>
+        <v>89.86880493164062</v>
       </c>
       <c r="C216" t="n">
         <v>92.69000244140625</v>
@@ -6283,7 +6283,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>108.5364456176758</v>
+        <v>108.5364379882812</v>
       </c>
       <c r="C219" t="n">
         <v>111.5800018310547</v>
@@ -6341,7 +6341,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>108.0695343017578</v>
+        <v>108.0695266723633</v>
       </c>
       <c r="C221" t="n">
         <v>111.0999984741211</v>
@@ -6370,7 +6370,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>101.0756607055664</v>
+        <v>101.0756683349609</v>
       </c>
       <c r="C222" t="n">
         <v>103.9100036621094</v>
@@ -6399,7 +6399,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>96.58168029785156</v>
+        <v>96.58167266845703</v>
       </c>
       <c r="C223" t="n">
         <v>99.29000091552734</v>
@@ -6428,7 +6428,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>91.55487060546875</v>
+        <v>91.55487823486328</v>
       </c>
       <c r="C224" t="n">
         <v>93.69000244140625</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>88.32030487060547</v>
+        <v>88.3203125</v>
       </c>
       <c r="C225" t="n">
         <v>90.37999725341797</v>
@@ -6602,7 +6602,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>110.9729995727539</v>
+        <v>110.9730072021484</v>
       </c>
       <c r="C230" t="n">
         <v>113.0599975585938</v>
@@ -6689,7 +6689,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>89.27113342285156</v>
+        <v>89.27114105224609</v>
       </c>
       <c r="C233" t="n">
         <v>90.94999694824219</v>
@@ -6776,7 +6776,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>117.4098815917969</v>
+        <v>117.4098892211914</v>
       </c>
       <c r="C236" t="n">
         <v>119.1100006103516</v>
@@ -6863,7 +6863,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>111.0125274658203</v>
+        <v>111.0125198364258</v>
       </c>
       <c r="C239" t="n">
         <v>112.620002746582</v>
@@ -6892,7 +6892,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>102.9788513183594</v>
+        <v>102.9788436889648</v>
       </c>
       <c r="C240" t="n">
         <v>104.4700012207031</v>
